--- a/data/processed/cleaned_dataset.xlsx
+++ b/data/processed/cleaned_dataset.xlsx
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Computing and informatics</t>
+          <t>Computing and Informatics</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
